--- a/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Easthill_20251031.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Easthill_20251031.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,6 +740,87 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AH252</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Natalie's - Orange Juice</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>24.50</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>49.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TN454</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Natalie's - Orange Mango</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>13.38</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>13.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TN380</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Natalie's - Strawberry Lemonade</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10.15</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>10.15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
